--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134348160</v>
+        <v>136818046</v>
       </c>
       <c r="B8" t="n">
-        <v>99103</v>
+        <v>58164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,41 +1425,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219788</v>
+        <v>103023</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>svinasjö, Upl</t>
+          <t>Skogsväg S Svinasjön, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621432</v>
+        <v>621585</v>
       </c>
       <c r="R8" t="n">
-        <v>6657364</v>
+        <v>6657128</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,22 +1488,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,34 +1512,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Wåge Gustafsson</t>
+          <t>Ragnar Hall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Wåge Gustafsson</t>
+          <t>Ragnar Hall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134348160</t>
+          <t>https://artportalen.se/Sighting/136818046</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134215147</v>
+        <v>134348160</v>
       </c>
       <c r="B9" t="n">
-        <v>99112</v>
+        <v>99103</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,16 +1546,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>219788</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1559,20 +1563,24 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svinasjön, Upl</t>
+          <t>svinasjö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621516</v>
+        <v>621432</v>
       </c>
       <c r="R9" t="n">
-        <v>6657276</v>
+        <v>6657364</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1601,7 +1609,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1619,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,33 +1628,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Wåge Gustafsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Wåge Gustafsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134215147</t>
+          <t>https://artportalen.se/Sighting/134348160</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134348161</v>
+        <v>134215147</v>
       </c>
       <c r="B10" t="n">
-        <v>106324</v>
+        <v>99112</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,41 +1663,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>svinasjö, Upl</t>
+          <t>Svinasjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621432</v>
+        <v>621516</v>
       </c>
       <c r="R10" t="n">
-        <v>6657364</v>
+        <v>6657276</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1717,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1727,7 +1732,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,27 +1747,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Wåge Gustafsson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Wåge Gustafsson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134348161</t>
+          <t>https://artportalen.se/Sighting/134215147</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134215145</v>
+        <v>134348161</v>
       </c>
       <c r="B11" t="n">
-        <v>98060</v>
+        <v>106324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,37 +1775,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svinasjön, Upl</t>
+          <t>svinasjö, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621525</v>
+        <v>621432</v>
       </c>
       <c r="R11" t="n">
-        <v>6657174</v>
+        <v>6657364</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1829,7 +1838,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1839,7 +1848,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,65 +1863,65 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Wåge Gustafsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Wåge Gustafsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134215145</t>
+          <t>https://artportalen.se/Sighting/134348161</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115432592</v>
+        <v>134215145</v>
       </c>
       <c r="B12" t="n">
-        <v>91859</v>
+        <v>98060</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Upl</t>
+          <t>Svinasjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621777</v>
+        <v>621525</v>
       </c>
       <c r="R12" t="n">
-        <v>6657403</v>
+        <v>6657174</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1936,27 +1945,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Under granlåga</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,71 +1975,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115432592</t>
+          <t>https://artportalen.se/Sighting/134215145</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123536725</v>
+        <v>115432592</v>
       </c>
       <c r="B13" t="n">
-        <v>96554</v>
+        <v>91859</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Galtström, Upl</t>
+          <t>Galtström, Galtström, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621737</v>
+        <v>621777</v>
       </c>
       <c r="R13" t="n">
-        <v>6657388</v>
+        <v>6657403</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2062,22 +2057,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Under granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2103,16 +2103,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123536725</t>
+          <t>https://artportalen.se/Sighting/115432592</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108911051</v>
+        <v>123536725</v>
       </c>
       <c r="B14" t="n">
-        <v>91872</v>
+        <v>96554</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,24 +2120,33 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Galtström, Upl</t>
@@ -2174,12 +2183,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2205,16 +2224,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108911051</t>
+          <t>https://artportalen.se/Sighting/123536725</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134215143</v>
+        <v>108911051</v>
       </c>
       <c r="B15" t="n">
-        <v>57162</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,34 +2241,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svinasjön, Upl</t>
+          <t>Galtström, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621672</v>
+        <v>621737</v>
       </c>
       <c r="R15" t="n">
-        <v>6657133</v>
+        <v>6657388</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2276,27 +2295,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2311,70 +2315,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134215143</t>
+          <t>https://artportalen.se/Sighting/108911051</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>64828530</v>
+        <v>134215143</v>
       </c>
       <c r="B16" t="n">
-        <v>5482</v>
+        <v>57162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101920</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupdalsåsen, N om, Upl</t>
+          <t>Svinasjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622165</v>
+        <v>621672</v>
       </c>
       <c r="R16" t="n">
-        <v>6657267</v>
+        <v>6657133</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2398,12 +2397,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2017-04-03</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2017-04-03</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,74 +2428,74 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>40 flyghål (över 10m stamved) på tallåga</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64828530</t>
+          <t>https://artportalen.se/Sighting/134215143</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134215144</v>
+        <v>64828530</v>
       </c>
       <c r="B17" t="n">
-        <v>57165</v>
+        <v>5482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102613</v>
+        <v>101920</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svinasjön, Upl</t>
+          <t>Djupdalsåsen, N om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621611</v>
+        <v>622165</v>
       </c>
       <c r="R17" t="n">
-        <v>6657149</v>
+        <v>6657267</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2505,27 +2519,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2017-04-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
+          <t>2017-04-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2536,66 +2535,71 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>40 flyghål (över 10m stamved) på tallåga</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134215144</t>
+          <t>https://artportalen.se/Sighting/64828530</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115432699</v>
+        <v>134215144</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>57165</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Upl</t>
+          <t>Svinasjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621798</v>
+        <v>621611</v>
       </c>
       <c r="R18" t="n">
-        <v>6657363</v>
+        <v>6657149</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2622,22 +2626,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2652,24 +2661,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115432699</t>
+          <t>https://artportalen.se/Sighting/134215144</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115432741</v>
+        <v>115432699</v>
       </c>
       <c r="B19" t="n">
         <v>99118</v>
@@ -2704,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621838</v>
+        <v>621798</v>
       </c>
       <c r="R19" t="n">
-        <v>6657388</v>
+        <v>6657363</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2739,7 +2748,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2749,12 +2758,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Några enstaka Bladrosetter</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2780,13 +2784,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115432741</t>
+          <t>https://artportalen.se/Sighting/115432699</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115432896</v>
+        <v>115432741</v>
       </c>
       <c r="B20" t="n">
         <v>99118</v>
@@ -2821,10 +2825,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>621784</v>
+        <v>621838</v>
       </c>
       <c r="R20" t="n">
-        <v>6657394</v>
+        <v>6657388</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2856,7 +2860,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2866,7 +2870,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Några enstaka Bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,13 +2901,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115432896</t>
+          <t>https://artportalen.se/Sighting/115432741</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115433059</v>
+        <v>115432896</v>
       </c>
       <c r="B21" t="n">
         <v>99118</v>
@@ -2933,10 +2942,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>621618</v>
+        <v>621784</v>
       </c>
       <c r="R21" t="n">
-        <v>6657241</v>
+        <v>6657394</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2968,7 +2977,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2978,7 +2987,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3003,6 +3012,118 @@
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115432896</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>115433059</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>621618</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6657241</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/115433059</t>
         </is>
@@ -3030,6 +3151,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1417,7 +1417,7 @@
         <v>136818046</v>
       </c>
       <c r="B8" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1417,7 +1417,7 @@
         <v>136818046</v>
       </c>
       <c r="B8" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1447,11 +1447,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skogsväg S Svinasjön, Heby-Råksjön, Upl</t>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1417,7 +1417,7 @@
         <v>136818046</v>
       </c>
       <c r="B8" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1417,7 +1417,7 @@
         <v>136818046</v>
       </c>
       <c r="B8" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1417,7 +1417,7 @@
         <v>136818046</v>
       </c>
       <c r="B8" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
